--- a/ig/DM-JUILLET-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14740" uniqueCount="9849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14761" uniqueCount="9863">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4870</t>
+    <t>4877</t>
   </si>
   <si>
     <t>Code</t>
@@ -7675,6 +7675,12 @@
     <t>ASDR/877/44/844</t>
   </si>
   <si>
+    <t>50739</t>
+  </si>
+  <si>
+    <t>ASDR/866/03/843</t>
+  </si>
+  <si>
     <t>60001</t>
   </si>
   <si>
@@ -23251,6 +23257,12 @@
     <t>AMSR/935/48/700</t>
   </si>
   <si>
+    <t>72536</t>
+  </si>
+  <si>
+    <t>AMSR/965/43/700</t>
+  </si>
+  <si>
     <t>80001</t>
   </si>
   <si>
@@ -29561,6 +29573,36 @@
   </si>
   <si>
     <t>ASOCR/941/11/861</t>
+  </si>
+  <si>
+    <t>81054</t>
+  </si>
+  <si>
+    <t>ASOCR/840/15/437</t>
+  </si>
+  <si>
+    <t>81055</t>
+  </si>
+  <si>
+    <t>ASOCR/840/48/442</t>
+  </si>
+  <si>
+    <t>81056</t>
+  </si>
+  <si>
+    <t>ASOCR/842/40/117</t>
+  </si>
+  <si>
+    <t>81058</t>
+  </si>
+  <si>
+    <t>ASOCR/916/11/831</t>
+  </si>
+  <si>
+    <t>81060</t>
+  </si>
+  <si>
+    <t>ASOCR/960/11/811</t>
   </si>
 </sst>
 </file>
@@ -30190,7 +30232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4871"/>
+  <dimension ref="A1:D4878"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -88647,6 +88689,90 @@
       </c>
       <c r="D4871" s="2"/>
     </row>
+    <row r="4872">
+      <c r="A4872" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4872" t="s" s="2">
+        <v>9849</v>
+      </c>
+      <c r="C4872" t="s" s="2">
+        <v>9850</v>
+      </c>
+      <c r="D4872" s="2"/>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4873" t="s" s="2">
+        <v>9851</v>
+      </c>
+      <c r="C4873" t="s" s="2">
+        <v>9852</v>
+      </c>
+      <c r="D4873" s="2"/>
+    </row>
+    <row r="4874">
+      <c r="A4874" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4874" t="s" s="2">
+        <v>9853</v>
+      </c>
+      <c r="C4874" t="s" s="2">
+        <v>9854</v>
+      </c>
+      <c r="D4874" s="2"/>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4875" t="s" s="2">
+        <v>9855</v>
+      </c>
+      <c r="C4875" t="s" s="2">
+        <v>9856</v>
+      </c>
+      <c r="D4875" s="2"/>
+    </row>
+    <row r="4876">
+      <c r="A4876" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4876" t="s" s="2">
+        <v>9857</v>
+      </c>
+      <c r="C4876" t="s" s="2">
+        <v>9858</v>
+      </c>
+      <c r="D4876" s="2"/>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4877" t="s" s="2">
+        <v>9859</v>
+      </c>
+      <c r="C4877" t="s" s="2">
+        <v>9860</v>
+      </c>
+      <c r="D4877" s="2"/>
+    </row>
+    <row r="4878">
+      <c r="A4878" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4878" t="s" s="2">
+        <v>9861</v>
+      </c>
+      <c r="C4878" t="s" s="2">
+        <v>9862</v>
+      </c>
+      <c r="D4878" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
